--- a/AAII_Financials/Quarterly/AIG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AIG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>AIG</t>
   </si>
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7093000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6638000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6595000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6413000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7055000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6548000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7104000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6689000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6517000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6717000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6530000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7315000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7309000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6683000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11790000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13998000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>13663000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>14944000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14087000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>12835000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10681000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>14454000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>9676000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10221000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9396000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>14443000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11852000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>12938000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>12591000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>12539000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>12653000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>11521000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>11667000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>11799000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>12667000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>11825000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>12563000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>12692000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>13129000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>12926000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4484000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4299000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4333000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4241000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4340000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4619000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4696000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4636000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4309000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4351000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4511000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4798000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4912000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4943000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1134000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1170000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1116000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1137000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1094000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1260000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>915000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1304000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>888000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>707000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>754000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1862000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1184000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1252000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1439000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1289000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1573000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1118000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1337000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1358000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1153000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>912000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1115000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1108000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>896000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1018000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2609000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2339000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2262000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2172000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2715000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1929000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2408000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2053000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2208000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2366000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2019000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2517000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2397000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1740000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10656000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>12828000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>12547000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>13807000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>12993000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>11575000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9766000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>13150000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>8788000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>9514000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8642000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>12581000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>10668000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>11686000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>11152000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>11250000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>11080000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>10403000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>10330000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>10441000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>11514000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>10913000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>11448000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>11584000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>12233000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>11908000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,175 +1467,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E14" s="3">
         <v>127000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>104000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>153000</v>
       </c>
-      <c r="G14" s="3">
-        <v>23000</v>
-      </c>
       <c r="H14" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="I14" s="3">
         <v>-3000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-394000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>145000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>325000</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>417000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-80000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>15000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>131000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-6000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>300000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-40000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-2696000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-51000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>107000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-15000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-130000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>22000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>8412000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>233000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>127000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>24000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>46000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>75000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>90000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>34000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>16000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>83000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-210000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>88000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>117000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>159000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>-77000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>-70000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>939000</v>
+      </c>
+      <c r="E15" s="3">
         <v>849000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>875000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>831000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>883000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>866000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>990000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>856000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>900000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>851000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>948000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>869000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>838000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1186000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5716000</v>
+      </c>
+      <c r="E17" s="3">
         <v>5402000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5687000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5436000</v>
       </c>
-      <c r="G17" s="3">
-        <v>5374000</v>
-      </c>
       <c r="H17" s="3">
+        <v>5452000</v>
+      </c>
+      <c r="I17" s="3">
         <v>5725000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5916000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5849000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5502000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5599000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5513000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6122000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6404000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6196000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10775000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9812000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9472000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8967000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8742000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10331000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10196000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9384000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9876000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9474000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>18692000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>11530000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10456000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>11330000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10394000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>11036000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>12941000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>12722000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>10116000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>10295000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>11504000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>14338000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>10604000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>10667000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>16279000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>11860000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1377000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1236000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>908000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>977000</v>
       </c>
-      <c r="G18" s="3">
-        <v>1681000</v>
-      </c>
       <c r="H18" s="3">
+        <v>1603000</v>
+      </c>
+      <c r="I18" s="3">
         <v>823000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1188000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>840000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1015000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1118000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1017000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1193000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>905000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>487000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1015000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4186000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4191000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5977000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5345000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2504000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>485000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5070000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-200000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>747000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-9296000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2913000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1396000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1608000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2197000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1503000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-288000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-1201000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1551000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1504000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1163000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-2513000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1959000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2025000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>-3150000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1066000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,56 +2056,57 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E20" s="3">
         <v>22000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>38000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>11000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>14000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-226000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-73000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-66000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-52000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-56000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>35000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-125000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-35000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>55000</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -2146,130 +2179,136 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2309000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2063000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1745000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1797000</v>
       </c>
-      <c r="G21" s="3">
-        <v>2550000</v>
-      </c>
       <c r="H21" s="3">
+        <v>2472000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1915000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2251000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1762000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1967000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2025000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1969000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2027000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1868000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1708000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2158000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5317000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5247000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7111000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6388000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3724000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1432000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6493000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>697000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1410000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-8614000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4791000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2569000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2784000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3555000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2802000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1261000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-172000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2953000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2886000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2231000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-1709000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>2949000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>3037000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>-1874000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1610000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2277,365 +2316,374 @@
         <v>100000</v>
       </c>
       <c r="E22" s="3">
+        <v>100000</v>
+      </c>
+      <c r="F22" s="3">
         <v>105000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>99000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>100000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>92000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>109000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>112000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>125000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>116000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>125000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>138000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>129000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>124000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>314000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>282000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>266000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>263000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>297000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>328000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>338000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>342000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>358000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>379000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>365000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>355000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>360000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>348000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>360000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>349000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>407000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>326000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>299000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>277000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>288000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>290000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>292000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>298000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>305000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>329000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1264000</v>
+      </c>
+      <c r="E23" s="3">
         <v>987000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>661000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>714000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1544000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>960000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1546000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>649000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>617000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1058000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>479000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1100000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>886000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>402000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>756000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3904000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3925000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5714000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5048000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2176000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>147000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4728000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-558000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>368000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-9661000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2558000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1036000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1260000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1837000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1154000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-695000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-1527000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1252000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1227000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>875000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-2803000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1667000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1727000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-3455000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>737000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>316000</v>
+      </c>
+      <c r="E24" s="3">
         <v>224000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-70000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>190000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>262000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>599000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>168000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>142000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>261000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-383000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>399000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>45000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>65000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>209000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>817000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>845000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1154000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>942000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>439000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-3000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>798000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-542000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>74000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1896000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>904000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>216000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>287000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>446000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>217000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-137000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-307000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>321000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>277000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>844000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-1091000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>557000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>516000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-985000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>304000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>948000</v>
+      </c>
+      <c r="E26" s="3">
         <v>763000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>731000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>524000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1144000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>698000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>947000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>481000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>475000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>797000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>862000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>701000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>841000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>337000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>547000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3087000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3080000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4560000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4106000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1737000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>150000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3930000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-16000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>294000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-7765000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1654000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>820000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>973000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1391000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>937000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-558000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-1220000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>931000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>950000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>31000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-1712000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1110000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1211000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-2470000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>433000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>948000</v>
+      </c>
+      <c r="E27" s="3">
         <v>763000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>735000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>519000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1144000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>698000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>898000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>459000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3977000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1194000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>86000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2020000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1485000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>23000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>545000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2741000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2747000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4166000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3739000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1660000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>91000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3869000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-60000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>276000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-7935000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1742000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>873000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>648000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1103000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>654000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-620000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-1220000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>937000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>939000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>43000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-1738000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1122000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1185000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-3005000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>459000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3143,41 +3203,41 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-46000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-24000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-4359000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>803000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-1335000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>2046000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>850000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-424000</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>-1000</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
         <v>0</v>
       </c>
@@ -3194,58 +3254,61 @@
         <v>0</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>5000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>49000</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-39000</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-6703000</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>8000</v>
       </c>
-      <c r="AN29" s="3">
-        <v>0</v>
-      </c>
       <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
         <v>-36000</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,56 +3554,59 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-22000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-38000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-11000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-14000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>226000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>73000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>66000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>52000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>56000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-35000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>125000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>35000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-55000</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -3610,130 +3679,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>948000</v>
+      </c>
+      <c r="E33" s="3">
         <v>763000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>735000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>519000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1144000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>698000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>898000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>459000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3977000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1216000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>93000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2027000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1493000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>30000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>545000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2741000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2746000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4166000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3739000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1660000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>91000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3869000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-60000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>281000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-7936000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1742000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>922000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>648000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1102000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>654000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-622000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-1259000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>937000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>938000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-6660000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-1739000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1130000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1185000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-3041000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>462000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>948000</v>
+      </c>
+      <c r="E35" s="3">
         <v>763000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>735000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>519000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1144000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>698000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>898000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>459000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3977000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1216000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>93000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2027000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1493000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>30000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>545000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2741000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2746000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4166000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3739000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1660000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>91000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3869000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-60000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>281000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-7936000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1742000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>922000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>648000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1102000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>654000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-622000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-1259000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>937000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>938000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-6660000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-1739000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1130000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1185000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-3041000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>462000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,175 +4276,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1490000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1454000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1274000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1589000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1825000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1393000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1302000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1472000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1381000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1816000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1540000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1994000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2283000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1923000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2043000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2294000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2378000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2537000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2198000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2699000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2760000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2796000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2827000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3191000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3408000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2738000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2856000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3361000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2935000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2565000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2873000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2741000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2135000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2103000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2362000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2433000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2517000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1918000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1868000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>2498000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>9005000</v>
+      </c>
+      <c r="E42" s="3">
         <v>8139000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>11086000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>9414000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>10100000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>10599000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>14407000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11776000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>12560000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>15073000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>12864000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>13044000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>10923000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>13148000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4435,130 +4524,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12761000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11634000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10441000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11264000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13013000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11684000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10463000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11196000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11669000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11293000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9967000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11388000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12428000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>15523000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13243000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13476000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>15000000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>14827000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>12409000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>13593000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>14303000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>13808000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>11333000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>11827000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>12829000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>12072000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>10274000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>11786000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>12614000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>12655000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>11011000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>12238000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>10860000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>11107000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>10248000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>11156000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>10921000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>11130000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>10465000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>11606000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4601,8 +4696,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,53 +4774,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>42062000</v>
+      </c>
+      <c r="E45" s="3">
         <v>42319000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>41135000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>41973000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>42306000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>41909000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>40865000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>43324000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>43599000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>75399000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>420536000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>85001000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>86724000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>76752000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>65393000</v>
+      </c>
+      <c r="E46" s="3">
         <v>63620000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>64007000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>64245000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>67260000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>65600000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>67107000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>67855000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>69230000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>103628000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>444940000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>111467000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>112427000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>107481000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,141 +5024,147 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>80014000</v>
+      </c>
+      <c r="E47" s="3">
         <v>79836000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>78716000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>81117000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>80344000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>77501000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>75024000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>81950000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>78575000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>252505000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>72727000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>236349000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>241980000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>248655000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>309946000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>306087000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>315062000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>337870000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>359292000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>355596000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>359539000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>348457000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>360668000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>356404000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>350151000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>332336000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>337615000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>340993000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>334928000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>324863000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>314209000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>316063000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>319758000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>322375000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>322292000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>321123000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>320746000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>315505000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>328175000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>346368000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="3">
         <v>690000</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>8</v>
@@ -5065,11 +5172,11 @@
       <c r="H48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3">
         <v>696000</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>8</v>
@@ -5077,11 +5184,11 @@
       <c r="L48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N48" s="3">
         <v>744000</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>8</v>
@@ -5089,8 +5196,8 @@
       <c r="P48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -5110,14 +5217,14 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-      <c r="X48" s="3" t="s">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>906000</v>
-      </c>
-      <c r="Z48" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>8</v>
@@ -5125,11 +5232,11 @@
       <c r="AB48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD48" s="3">
         <v>648000</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>724000</v>
       </c>
       <c r="AE48" s="3">
         <v>724000</v>
@@ -5137,8 +5244,8 @@
       <c r="AF48" s="3">
         <v>724000</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>8</v>
+      <c r="AG48" s="3">
+        <v>724000</v>
       </c>
       <c r="AH48" s="3" t="s">
         <v>8</v>
@@ -5149,8 +5256,8 @@
       <c r="AJ48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK48" s="3">
-        <v>0</v>
+      <c r="AK48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL48" s="3">
         <v>0</v>
@@ -5167,56 +5274,59 @@
       <c r="AP48" s="3">
         <v>0</v>
       </c>
+      <c r="AQ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5639000</v>
+      </c>
+      <c r="E49" s="3">
         <v>5546000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6225000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5574000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5604000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5407000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5808000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5644000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5530000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12111000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5933000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11999000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>12702000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13304000</v>
       </c>
-      <c r="Q49" s="3" t="s">
+      <c r="R49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
-      </c>
       <c r="S49" s="3">
         <v>0</v>
       </c>
@@ -5289,8 +5399,11 @@
       <c r="AP49" s="3">
         <v>0</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4943000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4666000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3633000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4598000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4521000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4657000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3863000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4436000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4640000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>109026000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4335000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>96172000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>104321000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>101877000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14837000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15319000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>14422000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>13475000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>11746000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>12443000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12870000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>13928000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>12847000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>13160000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>13541000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>14232000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>13389000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>13399000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>13569000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>14908000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>15564000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>15442000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>14980000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>14779000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>14350000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>21173000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>20492000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>27682000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>28724000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>25269000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>163464000</v>
+      </c>
+      <c r="E54" s="3">
         <v>161543000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>161254000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>163415000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>165971000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>161864000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>161322000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>169449000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>167890000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>544121000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>539306000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>521521000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>537138000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>536627000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>522228000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>522932000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>538938000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>573513000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>596112000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>594800000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>598250000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>584390000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>586481000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>577230000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>569388000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>510477000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>525064000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>525122000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>522269000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>512922000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>491984000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>504860000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>496829000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>499143000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>498301000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>503073000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>499762000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>500162000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>498264000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>514568000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,53 +6116,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>69852000</v>
+      </c>
+      <c r="E57" s="3">
         <v>69963000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>70666000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>69882000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>69754000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>68896000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>69168000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>71066000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>69783000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>70060000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>70393000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>69823000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>70284000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>75793000</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6109,23 +6239,26 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>966000</v>
+      </c>
+      <c r="E58" s="3">
         <v>28000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>165000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
@@ -6139,49 +6272,49 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>250000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>1000000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1525000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2132000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2143000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>61000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>51000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>67000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>68000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>34000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>90000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>390000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1896000</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>8</v>
@@ -6189,11 +6322,11 @@
       <c r="AB58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AC58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD58" s="3">
         <v>1536000</v>
-      </c>
-      <c r="AD58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>8</v>
@@ -6207,8 +6340,8 @@
       <c r="AH58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI58" s="3">
-        <v>0</v>
+      <c r="AI58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ58" s="3">
         <v>0</v>
@@ -6231,175 +6364,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>34476000</v>
+      </c>
+      <c r="E59" s="3">
         <v>32715000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>30522000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>32819000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>34765000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>32480000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>30073000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>32744000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>30583000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>57384000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>396450000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>61087000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>63695000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>56696000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>420102000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>426422000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>435632000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>456172000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>468333000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>464772000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>465576000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>454728000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>455626000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>446122000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>438666000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>384041000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>396411000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>395941000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>392360000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>388330000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>375499000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>384436000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>374189000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>375246000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>374903000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>371769000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>364664000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>360884000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>358092000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>361234000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>106800000</v>
+      </c>
+      <c r="E60" s="3">
         <v>104200000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>102909000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>104203000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>106357000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>103137000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>100763000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>105330000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>101761000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>127694000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>468194000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>131910000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>135504000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>134621000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,174 +6614,180 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8161000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9128000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9882000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9231000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9258000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8753000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9790000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10054000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9940000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>21685000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11500000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>23055000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>22620000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>23912000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>27179000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>55448000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>28387000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>29871000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>30095000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>31516000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>35637000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>35258000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>35638000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>38237000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>39280000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>35410000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>33814000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>35262000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>36291000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>35776000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>34540000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>34594000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>33784000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>33619000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>31640000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>31039000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>31812000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>30747000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>30912000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>32277000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7877000</v>
+      </c>
+      <c r="E62" s="3">
         <v>7786000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7301000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8864000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8827000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8515000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8219000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8992000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11714000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>345632000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8311000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>323343000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>332523000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>331788000</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>8</v>
@@ -6656,8 +6801,8 @@
       <c r="U62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="V62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
@@ -6708,19 +6853,22 @@
         <v>0</v>
       </c>
       <c r="AM62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN62" s="3">
         <v>827000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>5771000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>6106000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>3909000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>122838000</v>
+      </c>
+      <c r="E66" s="3">
         <v>121114000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>120092000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>122298000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>124442000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>120405000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>118772000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>124376000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>123415000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>495011000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>488005000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>478308000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>490647000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>490321000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>481258000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>483909000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>493594000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>517569000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>530156000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>529937000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>532167000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>521711000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>520119000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>513122000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>507154000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>450304000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>459389000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>459519000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>457730000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>452135000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>435623000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>446274000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>435643000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>436351000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>433130000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>430605000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>426030000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>426093000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>421964000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>425905000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7528,7 +7695,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
-        <v>485000</v>
+        <v>0</v>
       </c>
       <c r="N70" s="3">
         <v>485000</v>
@@ -7588,7 +7755,7 @@
         <v>485000</v>
       </c>
       <c r="AG70" s="3">
-        <v>0</v>
+        <v>485000</v>
       </c>
       <c r="AH70" s="3">
         <v>0</v>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>38388000</v>
+      </c>
+      <c r="E72" s="3">
         <v>37704000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>37186000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>36698000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>36424000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>35540000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>35079000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>34429000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>34225000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>38466000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>37516000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>37689000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>35916000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>34690000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>34893000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>33009000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>30550000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>27764000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>23785000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>20320000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>18935000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>19121000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>15504000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>15838000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>15847000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>24062000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>23084000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>22439000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>22077000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>21259000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>20884000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>21749000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>23318000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>22671000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>21457000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>28389000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>30420000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>29591000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>28711000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>32077000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>40606000</v>
+      </c>
+      <c r="E76" s="3">
         <v>40405000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>41139000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>41085000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>41501000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>41431000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>42521000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>45039000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>44445000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>43385000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>44866000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>39499000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>41969000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>42832000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>40485000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>38538000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>44859000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>55459000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>65471000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>64378000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>65598000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>62194000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>65877000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>63623000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>61749000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>59688000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>65190000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>65118000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>64054000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>60302000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>56361000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>58586000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>61186000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>62792000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>65171000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>72468000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>73732000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>74069000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>76300000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>88663000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>948000</v>
+      </c>
+      <c r="E81" s="3">
         <v>763000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>735000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>519000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1144000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>698000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>898000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>459000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3977000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1216000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>93000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2027000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1493000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>30000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>545000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2741000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2746000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4166000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3739000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1660000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>91000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3869000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-60000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>281000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-7936000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1742000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>922000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>648000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1102000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>654000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-622000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-1259000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>937000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>938000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-6660000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-1739000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1130000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1185000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-3041000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>462000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>878000</v>
+      </c>
+      <c r="E83" s="3">
         <v>862000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>972000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>856000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>900000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>851000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>948000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>869000</v>
       </c>
-      <c r="K83" s="3" t="s">
+      <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1186000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1088000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1131000</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1134000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>930000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1220000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1251000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1447000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1043000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1220000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>947000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1423000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>897000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>663000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>682000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1878000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1173000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1176000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1358000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1299000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1549000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1029000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1402000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1382000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1068000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>804000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>990000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>1012000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>1276000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>544000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1716000</v>
+      </c>
+      <c r="E89" s="3">
         <v>155000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>636000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1343000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1391000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-56000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>125000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1699000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>928000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>521000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1619000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3513000</v>
       </c>
-      <c r="O89" s="3" t="s">
+      <c r="P89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>497000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>190000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3386000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>575000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>57000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>951000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2518000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2170000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>640000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1194000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>907000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1330000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-202000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>483000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-296000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-976000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>99000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>302000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>598000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-938000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1044000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>241000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1314000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-10284000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>630000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1182000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,8 +9881,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9706,8 +9926,8 @@
       <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9784,8 +10004,11 @@
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-752000</v>
+      </c>
+      <c r="E94" s="3">
         <v>833000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-69000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-56000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>564000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>2751000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2653000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>315000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1602000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>306000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2948000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3432000</v>
       </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1474000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1361000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4799000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1681000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>853000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-356000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1279000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3150000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>1505000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-981000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2318000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2270000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-633000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-682000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-646000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2168000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1979000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>694000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>553000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>502000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1972000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-103000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-145000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>420000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>14499000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>4419000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>589000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,73 +10426,74 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>263000</v>
+      </c>
+      <c r="E96" s="3">
         <v>241000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>242000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>246000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>254000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>234000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>244000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>254000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>261000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>243000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>249000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>254000</v>
       </c>
-      <c r="O96" s="3" t="s">
+      <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>234000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-236000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-240000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-248000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-258000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-264000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-269000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-274000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-276000</v>
       </c>
       <c r="Y96" s="3">
         <v>-276000</v>
@@ -10269,55 +10502,58 @@
         <v>-276000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-276000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-275000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-276000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-279000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-278000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-279000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-278000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-280000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-283000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-286000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-289000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-288000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-287000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-290000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-307000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-321000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-338000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,370 +10924,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-799000</v>
+        <v>-920000</v>
       </c>
       <c r="E100" s="3">
         <v>-799000</v>
       </c>
       <c r="F100" s="3">
+        <v>-799000</v>
+      </c>
+      <c r="G100" s="3">
         <v>-1532000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1535000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2677000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3004000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1911000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>996000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1144000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1021000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-124000</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>817000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>917000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1240000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2182000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-577000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-975000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1460000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>814000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2114000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>153000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1201000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2472000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1232000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>424000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>737000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2454000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2764000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-539000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-90000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1063000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>2486000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-571000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-99000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-979000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-4048000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-5536000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-1107000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E101" s="3">
         <v>18000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-46000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>29000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-37000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-29000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>24000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-55000</v>
       </c>
-      <c r="K101" s="3" t="s">
+      <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-42000</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-48000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>3000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-59000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-13000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-27000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-6000</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-17000</v>
       </c>
       <c r="X101" s="3">
         <v>-17000</v>
       </c>
       <c r="Y101" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="Z101" s="3">
         <v>22000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>24000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>10000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-23000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>11000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>16000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>12000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-19000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-22000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-28000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>58000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>3000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>58000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-82000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-36000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>50000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E102" s="3">
         <v>183000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-249000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-247000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>433000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>36000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-272000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>132000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>285000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-346000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-284000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-98000</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-158000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-324000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-188000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>302000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-407000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-227000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-183000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>14000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-377000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-245000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>533000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>32000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-483000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>585000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>6000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-179000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>235000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>743000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-366000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>32000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-105000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>618000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>85000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-523000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>714000</v>
       </c>
     </row>
